--- a/backend/data/financials_by_company/0377.HK.xlsx
+++ b/backend/data/financials_by_company/0377.HK.xlsx
@@ -662,55 +662,55 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
+        <v>44561</v>
       </c>
       <c r="B2" t="n">
-        <v>-26775000</v>
+        <v>-907521.738489</v>
       </c>
       <c r="C2" t="n">
-        <v>0.25</v>
+        <v>0.024645</v>
       </c>
       <c r="D2" t="n">
-        <v>-519154000</v>
+        <v>-596011000</v>
       </c>
       <c r="E2" t="n">
-        <v>-107100000</v>
+        <v>-36824000</v>
       </c>
       <c r="F2" t="n">
-        <v>-107100000</v>
+        <v>-36824000</v>
       </c>
       <c r="G2" t="n">
-        <v>-1263380000</v>
+        <v>-1778008000</v>
       </c>
       <c r="H2" t="n">
-        <v>80011000</v>
+        <v>120293000</v>
       </c>
       <c r="I2" t="n">
-        <v>1140956000</v>
+        <v>3438342000</v>
       </c>
       <c r="J2" t="n">
-        <v>-626254000</v>
+        <v>-632835000</v>
       </c>
       <c r="K2" t="n">
-        <v>-706265000</v>
+        <v>-753128000</v>
       </c>
       <c r="L2" t="n">
-        <v>-556569000</v>
+        <v>-1094785000</v>
       </c>
       <c r="M2" t="n">
-        <v>557061000</v>
+        <v>1076139000</v>
       </c>
       <c r="N2" t="n">
-        <v>492000</v>
+        <v>2560000</v>
       </c>
       <c r="O2" t="n">
-        <v>-1183055000</v>
+        <v>-1742091521.738489</v>
       </c>
       <c r="P2" t="n">
-        <v>-1263380000</v>
+        <v>-1778008000</v>
       </c>
       <c r="Q2" t="n">
-        <v>1351877000</v>
+        <v>3845907000</v>
       </c>
       <c r="R2" t="n">
         <v>61543075</v>
@@ -719,142 +719,144 @@
         <v>61543075</v>
       </c>
       <c r="T2" t="n">
-        <v>-20.53</v>
+        <v>-28.89</v>
       </c>
       <c r="U2" t="n">
-        <v>-20.53</v>
+        <v>-28.89</v>
       </c>
       <c r="V2" t="n">
-        <v>-1263380000</v>
+        <v>-1778008000</v>
       </c>
       <c r="W2" t="n">
-        <v>-1263380000</v>
+        <v>-1778008000</v>
       </c>
       <c r="X2" t="n">
         <v>0</v>
       </c>
       <c r="Y2" t="n">
-        <v>-1263380000</v>
+        <v>-1778008000</v>
       </c>
       <c r="Z2" t="n">
-        <v>985000</v>
+        <v>6177000</v>
       </c>
       <c r="AA2" t="n">
-        <v>-1264365000</v>
+        <v>-1784185000</v>
       </c>
       <c r="AB2" t="n">
-        <v>-1264365000</v>
+        <v>-1784185000</v>
       </c>
       <c r="AC2" t="n">
-        <v>1039000</v>
+        <v>-45082000</v>
       </c>
       <c r="AD2" t="n">
-        <v>5230000</v>
+        <v>8030000</v>
       </c>
       <c r="AE2" t="n">
-        <v>-107033000</v>
+        <v>-31628000</v>
       </c>
       <c r="AF2" t="n">
-        <v>-1081000</v>
+        <v>-31252000</v>
       </c>
       <c r="AG2" t="n">
-        <v>102479000</v>
+        <v>-18741000</v>
       </c>
       <c r="AH2" t="n">
-        <v>8564000</v>
+        <v>58123000</v>
       </c>
       <c r="AI2" t="n">
-        <v>-2929000</v>
+        <v>23498000</v>
       </c>
       <c r="AJ2" t="n">
-        <v>-556569000</v>
-      </c>
-      <c r="AK2" t="inlineStr"/>
+        <v>-1094785000</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>21206000</v>
+      </c>
       <c r="AL2" t="n">
-        <v>557061000</v>
+        <v>1076139000</v>
       </c>
       <c r="AM2" t="n">
-        <v>492000</v>
+        <v>2560000</v>
       </c>
       <c r="AN2" t="n">
-        <v>-196933000</v>
+        <v>-333469000</v>
       </c>
       <c r="AO2" t="n">
-        <v>210921000</v>
+        <v>407565000</v>
       </c>
       <c r="AP2" t="n">
-        <v>211371000</v>
+        <v>407565000</v>
       </c>
       <c r="AQ2" t="n">
-        <v>58421000</v>
+        <v>102371000</v>
       </c>
       <c r="AR2" t="n">
-        <v>152950000</v>
+        <v>305194000</v>
       </c>
       <c r="AS2" t="n">
-        <v>13988000</v>
+        <v>74096000</v>
       </c>
       <c r="AT2" t="n">
-        <v>1140956000</v>
+        <v>3438342000</v>
       </c>
       <c r="AU2" t="n">
-        <v>1154944000</v>
+        <v>3512438000</v>
       </c>
       <c r="AV2" t="n">
-        <v>1154944000</v>
+        <v>3512438000</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45291</v>
+        <v>44926</v>
       </c>
       <c r="B3" t="n">
-        <v>-7783680.87369</v>
+        <v>76521250</v>
       </c>
       <c r="C3" t="n">
-        <v>0.010236</v>
+        <v>0.25</v>
       </c>
       <c r="D3" t="n">
-        <v>-969679000</v>
+        <v>-1698927000</v>
       </c>
       <c r="E3" t="n">
-        <v>-760394000</v>
+        <v>306085000</v>
       </c>
       <c r="F3" t="n">
-        <v>-760394000</v>
+        <v>306085000</v>
       </c>
       <c r="G3" t="n">
-        <v>-2679371000</v>
+        <v>-2822338000</v>
       </c>
       <c r="H3" t="n">
-        <v>88884000</v>
+        <v>106845000</v>
       </c>
       <c r="I3" t="n">
-        <v>2752444000</v>
+        <v>1985902000</v>
       </c>
       <c r="J3" t="n">
-        <v>-1730073000</v>
+        <v>-1392842000</v>
       </c>
       <c r="K3" t="n">
-        <v>-1818957000</v>
+        <v>-1499687000</v>
       </c>
       <c r="L3" t="n">
-        <v>-879245000</v>
+        <v>-1304855000</v>
       </c>
       <c r="M3" t="n">
-        <v>879849000</v>
+        <v>1305536000</v>
       </c>
       <c r="N3" t="n">
-        <v>604000</v>
+        <v>681000</v>
       </c>
       <c r="O3" t="n">
-        <v>-1926760680.87369</v>
+        <v>-3051901750</v>
       </c>
       <c r="P3" t="n">
-        <v>-2679371000</v>
+        <v>-2822338000</v>
       </c>
       <c r="Q3" t="n">
-        <v>2998930000</v>
+        <v>2291098000</v>
       </c>
       <c r="R3" t="n">
         <v>61543075</v>
@@ -863,142 +865,142 @@
         <v>61543075</v>
       </c>
       <c r="T3" t="n">
-        <v>-43.54</v>
+        <v>-45.86</v>
       </c>
       <c r="U3" t="n">
-        <v>-43.54</v>
+        <v>-45.86</v>
       </c>
       <c r="V3" t="n">
-        <v>-2679371000</v>
+        <v>-2822338000</v>
       </c>
       <c r="W3" t="n">
-        <v>-2679371000</v>
+        <v>-2822338000</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>-2679371000</v>
+        <v>-2822338000</v>
       </c>
       <c r="Z3" t="n">
-        <v>-8191000</v>
+        <v>6053000</v>
       </c>
       <c r="AA3" t="n">
-        <v>-2671180000</v>
+        <v>-2828391000</v>
       </c>
       <c r="AB3" t="n">
-        <v>-2671180000</v>
+        <v>-2828391000</v>
       </c>
       <c r="AC3" t="n">
-        <v>-27626000</v>
+        <v>23168000</v>
       </c>
       <c r="AD3" t="n">
-        <v>4984000</v>
+        <v>4169000</v>
       </c>
       <c r="AE3" t="n">
-        <v>-760156000</v>
+        <v>308215000</v>
       </c>
       <c r="AF3" t="n">
-        <v>13625000</v>
+        <v>-606842000</v>
       </c>
       <c r="AG3" t="n">
-        <v>683917000</v>
+        <v>80929000</v>
       </c>
       <c r="AH3" t="n">
-        <v>69877000</v>
+        <v>217698000</v>
       </c>
       <c r="AI3" t="n">
-        <v>-7263000</v>
+        <v>0</v>
       </c>
       <c r="AJ3" t="n">
-        <v>-879245000</v>
+        <v>-1304855000</v>
       </c>
       <c r="AK3" t="inlineStr"/>
       <c r="AL3" t="n">
-        <v>879849000</v>
+        <v>1305536000</v>
       </c>
       <c r="AM3" t="n">
-        <v>604000</v>
+        <v>681000</v>
       </c>
       <c r="AN3" t="n">
-        <v>-154119000</v>
+        <v>-649920000</v>
       </c>
       <c r="AO3" t="n">
-        <v>246486000</v>
+        <v>305196000</v>
       </c>
       <c r="AP3" t="n">
-        <v>248746000</v>
+        <v>307596000</v>
       </c>
       <c r="AQ3" t="n">
-        <v>64789000</v>
+        <v>74753000</v>
       </c>
       <c r="AR3" t="n">
-        <v>183957000</v>
+        <v>232843000</v>
       </c>
       <c r="AS3" t="n">
-        <v>92367000</v>
+        <v>-344724000</v>
       </c>
       <c r="AT3" t="n">
-        <v>2752444000</v>
+        <v>1985902000</v>
       </c>
       <c r="AU3" t="n">
-        <v>2844811000</v>
+        <v>1641178000</v>
       </c>
       <c r="AV3" t="n">
-        <v>2844811000</v>
+        <v>1641178000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44926</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
-        <v>76521250</v>
+        <v>-7783680.87369</v>
       </c>
       <c r="C4" t="n">
-        <v>0.25</v>
+        <v>0.010236</v>
       </c>
       <c r="D4" t="n">
-        <v>-1698927000</v>
+        <v>-969679000</v>
       </c>
       <c r="E4" t="n">
-        <v>306085000</v>
+        <v>-760394000</v>
       </c>
       <c r="F4" t="n">
-        <v>306085000</v>
+        <v>-760394000</v>
       </c>
       <c r="G4" t="n">
-        <v>-2822338000</v>
+        <v>-2679371000</v>
       </c>
       <c r="H4" t="n">
-        <v>106845000</v>
+        <v>88884000</v>
       </c>
       <c r="I4" t="n">
-        <v>1985902000</v>
+        <v>2752444000</v>
       </c>
       <c r="J4" t="n">
-        <v>-1392842000</v>
+        <v>-1730073000</v>
       </c>
       <c r="K4" t="n">
-        <v>-1499687000</v>
+        <v>-1818957000</v>
       </c>
       <c r="L4" t="n">
-        <v>-1304855000</v>
+        <v>-879245000</v>
       </c>
       <c r="M4" t="n">
-        <v>1305536000</v>
+        <v>879849000</v>
       </c>
       <c r="N4" t="n">
-        <v>681000</v>
+        <v>604000</v>
       </c>
       <c r="O4" t="n">
-        <v>-3051901750</v>
+        <v>-1926760680.87369</v>
       </c>
       <c r="P4" t="n">
-        <v>-2822338000</v>
+        <v>-2679371000</v>
       </c>
       <c r="Q4" t="n">
-        <v>2291098000</v>
+        <v>2998930000</v>
       </c>
       <c r="R4" t="n">
         <v>61543075</v>
@@ -1007,142 +1009,142 @@
         <v>61543075</v>
       </c>
       <c r="T4" t="n">
-        <v>-45.86</v>
+        <v>-43.54</v>
       </c>
       <c r="U4" t="n">
-        <v>-45.86</v>
+        <v>-43.54</v>
       </c>
       <c r="V4" t="n">
-        <v>-2822338000</v>
+        <v>-2679371000</v>
       </c>
       <c r="W4" t="n">
-        <v>-2822338000</v>
+        <v>-2679371000</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>-2822338000</v>
+        <v>-2679371000</v>
       </c>
       <c r="Z4" t="n">
-        <v>6053000</v>
+        <v>-8191000</v>
       </c>
       <c r="AA4" t="n">
-        <v>-2828391000</v>
+        <v>-2671180000</v>
       </c>
       <c r="AB4" t="n">
-        <v>-2828391000</v>
+        <v>-2671180000</v>
       </c>
       <c r="AC4" t="n">
-        <v>23168000</v>
+        <v>-27626000</v>
       </c>
       <c r="AD4" t="n">
-        <v>4169000</v>
+        <v>4984000</v>
       </c>
       <c r="AE4" t="n">
-        <v>308215000</v>
+        <v>-760156000</v>
       </c>
       <c r="AF4" t="n">
-        <v>-606842000</v>
+        <v>13625000</v>
       </c>
       <c r="AG4" t="n">
-        <v>80929000</v>
+        <v>683917000</v>
       </c>
       <c r="AH4" t="n">
-        <v>217698000</v>
+        <v>69877000</v>
       </c>
       <c r="AI4" t="n">
-        <v>0</v>
+        <v>-7263000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>-1304855000</v>
+        <v>-879245000</v>
       </c>
       <c r="AK4" t="inlineStr"/>
       <c r="AL4" t="n">
-        <v>1305536000</v>
+        <v>879849000</v>
       </c>
       <c r="AM4" t="n">
-        <v>681000</v>
+        <v>604000</v>
       </c>
       <c r="AN4" t="n">
-        <v>-649920000</v>
+        <v>-154119000</v>
       </c>
       <c r="AO4" t="n">
-        <v>305196000</v>
+        <v>246486000</v>
       </c>
       <c r="AP4" t="n">
-        <v>307596000</v>
+        <v>248746000</v>
       </c>
       <c r="AQ4" t="n">
-        <v>74753000</v>
+        <v>64789000</v>
       </c>
       <c r="AR4" t="n">
-        <v>232843000</v>
+        <v>183957000</v>
       </c>
       <c r="AS4" t="n">
-        <v>-344724000</v>
+        <v>92367000</v>
       </c>
       <c r="AT4" t="n">
-        <v>1985902000</v>
+        <v>2752444000</v>
       </c>
       <c r="AU4" t="n">
-        <v>1641178000</v>
+        <v>2844811000</v>
       </c>
       <c r="AV4" t="n">
-        <v>1641178000</v>
+        <v>2844811000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44561</v>
+        <v>45657</v>
       </c>
       <c r="B5" t="n">
-        <v>-907521.738489</v>
+        <v>-26775000</v>
       </c>
       <c r="C5" t="n">
-        <v>0.024645</v>
+        <v>0.25</v>
       </c>
       <c r="D5" t="n">
-        <v>-596011000</v>
+        <v>-519154000</v>
       </c>
       <c r="E5" t="n">
-        <v>-36824000</v>
+        <v>-107100000</v>
       </c>
       <c r="F5" t="n">
-        <v>-36824000</v>
+        <v>-107100000</v>
       </c>
       <c r="G5" t="n">
-        <v>-1778008000</v>
+        <v>-1263380000</v>
       </c>
       <c r="H5" t="n">
-        <v>120293000</v>
+        <v>80011000</v>
       </c>
       <c r="I5" t="n">
-        <v>3438342000</v>
+        <v>1140956000</v>
       </c>
       <c r="J5" t="n">
-        <v>-632835000</v>
+        <v>-626254000</v>
       </c>
       <c r="K5" t="n">
-        <v>-753128000</v>
+        <v>-706265000</v>
       </c>
       <c r="L5" t="n">
-        <v>-1094785000</v>
+        <v>-556569000</v>
       </c>
       <c r="M5" t="n">
-        <v>1076139000</v>
+        <v>557061000</v>
       </c>
       <c r="N5" t="n">
-        <v>2560000</v>
+        <v>492000</v>
       </c>
       <c r="O5" t="n">
-        <v>-1742091521.738489</v>
+        <v>-1183055000</v>
       </c>
       <c r="P5" t="n">
-        <v>-1778008000</v>
+        <v>-1263380000</v>
       </c>
       <c r="Q5" t="n">
-        <v>3845907000</v>
+        <v>1351877000</v>
       </c>
       <c r="R5" t="n">
         <v>61543075</v>
@@ -1151,91 +1153,89 @@
         <v>61543075</v>
       </c>
       <c r="T5" t="n">
-        <v>-28.89</v>
+        <v>-20.53</v>
       </c>
       <c r="U5" t="n">
-        <v>-28.89</v>
+        <v>-20.53</v>
       </c>
       <c r="V5" t="n">
-        <v>-1778008000</v>
+        <v>-1263380000</v>
       </c>
       <c r="W5" t="n">
-        <v>-1778008000</v>
+        <v>-1263380000</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>-1778008000</v>
+        <v>-1263380000</v>
       </c>
       <c r="Z5" t="n">
-        <v>6177000</v>
+        <v>985000</v>
       </c>
       <c r="AA5" t="n">
-        <v>-1784185000</v>
+        <v>-1264365000</v>
       </c>
       <c r="AB5" t="n">
-        <v>-1784185000</v>
+        <v>-1264365000</v>
       </c>
       <c r="AC5" t="n">
-        <v>-45082000</v>
+        <v>1039000</v>
       </c>
       <c r="AD5" t="n">
-        <v>8030000</v>
+        <v>5230000</v>
       </c>
       <c r="AE5" t="n">
-        <v>-31628000</v>
+        <v>-107033000</v>
       </c>
       <c r="AF5" t="n">
-        <v>-31252000</v>
+        <v>-1081000</v>
       </c>
       <c r="AG5" t="n">
-        <v>-18741000</v>
+        <v>102479000</v>
       </c>
       <c r="AH5" t="n">
-        <v>58123000</v>
+        <v>8564000</v>
       </c>
       <c r="AI5" t="n">
-        <v>23498000</v>
+        <v>-2929000</v>
       </c>
       <c r="AJ5" t="n">
-        <v>-1094785000</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>21206000</v>
-      </c>
+        <v>-556569000</v>
+      </c>
+      <c r="AK5" t="inlineStr"/>
       <c r="AL5" t="n">
-        <v>1076139000</v>
+        <v>557061000</v>
       </c>
       <c r="AM5" t="n">
-        <v>2560000</v>
+        <v>492000</v>
       </c>
       <c r="AN5" t="n">
-        <v>-333469000</v>
+        <v>-196933000</v>
       </c>
       <c r="AO5" t="n">
-        <v>407565000</v>
+        <v>210921000</v>
       </c>
       <c r="AP5" t="n">
-        <v>407565000</v>
+        <v>211371000</v>
       </c>
       <c r="AQ5" t="n">
-        <v>102371000</v>
+        <v>58421000</v>
       </c>
       <c r="AR5" t="n">
-        <v>305194000</v>
+        <v>152950000</v>
       </c>
       <c r="AS5" t="n">
-        <v>74096000</v>
+        <v>13988000</v>
       </c>
       <c r="AT5" t="n">
-        <v>3438342000</v>
+        <v>1140956000</v>
       </c>
       <c r="AU5" t="n">
-        <v>3512438000</v>
+        <v>1154944000</v>
       </c>
       <c r="AV5" t="n">
-        <v>3512438000</v>
+        <v>1154944000</v>
       </c>
     </row>
   </sheetData>
@@ -1631,56 +1631,58 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
+        <v>44561</v>
       </c>
       <c r="B2" t="n">
-        <v>61543075</v>
+        <v>61543000</v>
       </c>
       <c r="C2" t="n">
-        <v>61543075</v>
+        <v>61543000</v>
       </c>
       <c r="D2" t="n">
-        <v>4978046000</v>
+        <v>10948747000</v>
       </c>
       <c r="E2" t="n">
-        <v>5017853000</v>
+        <v>11112752000</v>
       </c>
       <c r="F2" t="n">
-        <v>-7621857000</v>
+        <v>-850618000</v>
       </c>
       <c r="G2" t="n">
-        <v>-2607519000</v>
+        <v>10250333000</v>
       </c>
       <c r="H2" t="n">
-        <v>-10241444000</v>
+        <v>-7416620000</v>
       </c>
       <c r="I2" t="n">
-        <v>-7621857000</v>
+        <v>-850618000</v>
       </c>
       <c r="J2" t="n">
-        <v>3515000</v>
+        <v>11801000</v>
       </c>
       <c r="K2" t="n">
-        <v>-7621857000</v>
+        <v>-850618000</v>
       </c>
       <c r="L2" t="n">
-        <v>-7621857000</v>
+        <v>-591011000</v>
       </c>
       <c r="M2" t="n">
-        <v>-7586267000</v>
+        <v>-844868000</v>
       </c>
       <c r="N2" t="n">
-        <v>35590000</v>
+        <v>5750000</v>
       </c>
       <c r="O2" t="n">
-        <v>-7621857000</v>
+        <v>-850618000</v>
       </c>
       <c r="P2" t="n">
-        <v>29930000</v>
-      </c>
-      <c r="Q2" t="inlineStr"/>
+        <v>30185000</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>140000</v>
+      </c>
       <c r="R2" t="n">
-        <v>-11442307000</v>
+        <v>-4628951000</v>
       </c>
       <c r="S2" t="n">
         <v>2557466000</v>
@@ -1692,79 +1694,85 @@
         <v>55983000</v>
       </c>
       <c r="V2" t="n">
-        <v>12420778000</v>
+        <v>16580618000</v>
       </c>
       <c r="W2" t="n">
-        <v>144178000</v>
-      </c>
-      <c r="X2" t="inlineStr"/>
+        <v>593919000</v>
+      </c>
+      <c r="X2" t="n">
+        <v>187560000</v>
+      </c>
       <c r="Y2" t="n">
-        <v>130852000</v>
+        <v>133858000</v>
       </c>
       <c r="Z2" t="n">
-        <v>11973000</v>
+        <v>12036000</v>
       </c>
       <c r="AA2" t="n">
-        <v>1353000</v>
+        <v>260465000</v>
       </c>
       <c r="AB2" t="n">
-        <v>1353000</v>
+        <v>858000</v>
       </c>
       <c r="AC2" t="n">
-        <v>0</v>
+        <v>259607000</v>
       </c>
       <c r="AD2" t="n">
-        <v>12276600000</v>
+        <v>15986699000</v>
       </c>
       <c r="AE2" t="n">
-        <v>64326000</v>
+        <v>74518000</v>
       </c>
       <c r="AF2" t="n">
-        <v>5016500000</v>
+        <v>10852287000</v>
       </c>
       <c r="AG2" t="n">
-        <v>2162000</v>
+        <v>10943000</v>
       </c>
       <c r="AH2" t="n">
-        <v>5014338000</v>
+        <v>10841344000</v>
       </c>
       <c r="AI2" t="n">
-        <v>6527369000</v>
+        <v>3460756000</v>
       </c>
       <c r="AJ2" t="n">
-        <v>6118522000</v>
+        <v>2976487000</v>
       </c>
       <c r="AK2" t="n">
-        <v>217628000</v>
+        <v>172002000</v>
       </c>
       <c r="AL2" t="n">
-        <v>191219000</v>
+        <v>312267000</v>
       </c>
       <c r="AM2" t="n">
-        <v>4834511000</v>
+        <v>15735750000</v>
       </c>
       <c r="AN2" t="n">
-        <v>2799355000</v>
+        <v>7165671000</v>
       </c>
       <c r="AO2" t="n">
-        <v>3139000</v>
+        <v>2824000</v>
       </c>
       <c r="AP2" t="n">
-        <v>5842000</v>
-      </c>
-      <c r="AQ2" t="inlineStr"/>
-      <c r="AR2" t="inlineStr"/>
+        <v>7026000</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>23001000</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>23001000</v>
+      </c>
       <c r="AS2" t="n">
-        <v>31217000</v>
+        <v>30246000</v>
       </c>
       <c r="AT2" t="n">
         <v>0</v>
       </c>
       <c r="AU2" t="n">
-        <v>31217000</v>
+        <v>30246000</v>
       </c>
       <c r="AV2" t="n">
-        <v>1385836000</v>
+        <v>5075502000</v>
       </c>
       <c r="AW2" t="n">
         <v>0</v>
@@ -1773,81 +1781,87 @@
         <v>0</v>
       </c>
       <c r="AY2" t="n">
-        <v>1373321000</v>
+        <v>1973441000</v>
       </c>
       <c r="AZ2" t="n">
-        <v>-1724370000</v>
+        <v>-1263490000</v>
       </c>
       <c r="BA2" t="n">
-        <v>3097691000</v>
+        <v>3236931000</v>
       </c>
       <c r="BB2" t="n">
-        <v>955379000</v>
-      </c>
-      <c r="BC2" t="inlineStr"/>
+        <v>984248000</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>1932482000</v>
+      </c>
       <c r="BD2" t="n">
-        <v>1089297000</v>
+        <v>1073341000</v>
       </c>
       <c r="BE2" t="n">
-        <v>740290000</v>
+        <v>838704000</v>
       </c>
       <c r="BF2" t="n">
-        <v>312725000</v>
+        <v>340638000</v>
       </c>
       <c r="BG2" t="n">
         <v>0</v>
       </c>
       <c r="BH2" t="n">
-        <v>2035156000</v>
+        <v>8570079000</v>
       </c>
       <c r="BI2" t="n">
-        <v>106901000</v>
+        <v>59139000</v>
       </c>
       <c r="BJ2" t="n">
-        <v>15135000</v>
+        <v>18449000</v>
       </c>
       <c r="BK2" t="n">
-        <v>926618000</v>
+        <v>707571000</v>
       </c>
       <c r="BL2" t="n">
-        <v>844597000</v>
-      </c>
-      <c r="BM2" t="inlineStr"/>
+        <v>7376317000</v>
+      </c>
+      <c r="BM2" t="n">
+        <v>285077000</v>
+      </c>
       <c r="BN2" t="n">
-        <v>804006000</v>
+        <v>7298194000</v>
       </c>
       <c r="BO2" t="n">
-        <v>9076000</v>
+        <v>18817000</v>
       </c>
       <c r="BP2" t="n">
-        <v>31515000</v>
-      </c>
-      <c r="BQ2" t="inlineStr"/>
+        <v>59306000</v>
+      </c>
+      <c r="BQ2" t="n">
+        <v>5739000</v>
+      </c>
       <c r="BR2" t="n">
-        <v>105095000</v>
+        <v>945496000</v>
       </c>
       <c r="BS2" t="n">
-        <v>-105040000</v>
+        <v>-52234000</v>
       </c>
       <c r="BT2" t="n">
-        <v>210135000</v>
+        <v>290159000</v>
       </c>
       <c r="BU2" t="n">
-        <v>36810000</v>
+        <v>164939000</v>
       </c>
       <c r="BV2" t="n">
-        <v>518000</v>
+        <v>12735000</v>
       </c>
       <c r="BW2" t="n">
-        <v>36292000</v>
+        <v>152204000</v>
       </c>
       <c r="BX2" t="n">
-        <v>36292000</v>
+        <v>152204000</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45291</v>
+        <v>44926</v>
       </c>
       <c r="B3" t="n">
         <v>61543000</v>
@@ -1856,47 +1870,49 @@
         <v>61543000</v>
       </c>
       <c r="D3" t="n">
-        <v>5001585000</v>
+        <v>6754384000</v>
       </c>
       <c r="E3" t="n">
-        <v>5075071000</v>
+        <v>6818021000</v>
       </c>
       <c r="F3" t="n">
-        <v>-6350809000</v>
+        <v>-3695483000</v>
       </c>
       <c r="G3" t="n">
-        <v>-1283873000</v>
+        <v>3118640000</v>
       </c>
       <c r="H3" t="n">
-        <v>-9453660000</v>
+        <v>-8987107000</v>
       </c>
       <c r="I3" t="n">
-        <v>-6350809000</v>
+        <v>-3695483000</v>
       </c>
       <c r="J3" t="n">
-        <v>8135000</v>
+        <v>3898000</v>
       </c>
       <c r="K3" t="n">
-        <v>-6350809000</v>
+        <v>-3695483000</v>
       </c>
       <c r="L3" t="n">
-        <v>-6344800000</v>
+        <v>-3616272000</v>
       </c>
       <c r="M3" t="n">
-        <v>-6314233000</v>
+        <v>-3667098000</v>
       </c>
       <c r="N3" t="n">
-        <v>36576000</v>
+        <v>28385000</v>
       </c>
       <c r="O3" t="n">
-        <v>-6350809000</v>
+        <v>-3695483000</v>
       </c>
       <c r="P3" t="n">
-        <v>29936000</v>
-      </c>
-      <c r="Q3" t="inlineStr"/>
+        <v>30001000</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>140000</v>
+      </c>
       <c r="R3" t="n">
-        <v>-10178933000</v>
+        <v>-7499627000</v>
       </c>
       <c r="S3" t="n">
         <v>2557466000</v>
@@ -1908,83 +1924,83 @@
         <v>55983000</v>
       </c>
       <c r="V3" t="n">
-        <v>11952189000</v>
+        <v>14772157000</v>
       </c>
       <c r="W3" t="n">
-        <v>154012000</v>
+        <v>224452000</v>
       </c>
       <c r="X3" t="inlineStr"/>
       <c r="Y3" t="n">
-        <v>131486000</v>
+        <v>131656000</v>
       </c>
       <c r="Z3" t="n">
-        <v>11678000</v>
+        <v>11907000</v>
       </c>
       <c r="AA3" t="n">
-        <v>10848000</v>
+        <v>80889000</v>
       </c>
       <c r="AB3" t="n">
-        <v>4839000</v>
+        <v>1678000</v>
       </c>
       <c r="AC3" t="n">
-        <v>6009000</v>
+        <v>79211000</v>
       </c>
       <c r="AD3" t="n">
-        <v>11798177000</v>
+        <v>14547705000</v>
       </c>
       <c r="AE3" t="n">
-        <v>67255000</v>
+        <v>74518000</v>
       </c>
       <c r="AF3" t="n">
-        <v>5064223000</v>
+        <v>6737132000</v>
       </c>
       <c r="AG3" t="n">
-        <v>3296000</v>
+        <v>2220000</v>
       </c>
       <c r="AH3" t="n">
-        <v>5060927000</v>
+        <v>6734912000</v>
       </c>
       <c r="AI3" t="n">
-        <v>6038290000</v>
+        <v>6179944000</v>
       </c>
       <c r="AJ3" t="n">
-        <v>5629241000</v>
+        <v>5722404000</v>
       </c>
       <c r="AK3" t="n">
-        <v>204059000</v>
+        <v>226086000</v>
       </c>
       <c r="AL3" t="n">
-        <v>204990000</v>
+        <v>231454000</v>
       </c>
       <c r="AM3" t="n">
-        <v>5637956000</v>
+        <v>11105059000</v>
       </c>
       <c r="AN3" t="n">
-        <v>3293439000</v>
+        <v>5544461000</v>
       </c>
       <c r="AO3" t="n">
         <v>3082000</v>
       </c>
       <c r="AP3" t="n">
-        <v>5662000</v>
+        <v>6072000</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0</v>
+        <v>13220000</v>
       </c>
       <c r="AR3" t="n">
-        <v>0</v>
+        <v>13220000</v>
       </c>
       <c r="AS3" t="n">
-        <v>31067000</v>
+        <v>30638000</v>
       </c>
       <c r="AT3" t="n">
         <v>0</v>
       </c>
       <c r="AU3" t="n">
-        <v>31067000</v>
+        <v>30638000</v>
       </c>
       <c r="AV3" t="n">
-        <v>1793535000</v>
+        <v>3869392000</v>
       </c>
       <c r="AW3" t="n">
         <v>0</v>
@@ -1993,83 +2009,83 @@
         <v>0</v>
       </c>
       <c r="AY3" t="n">
-        <v>1460093000</v>
+        <v>1608573000</v>
       </c>
       <c r="AZ3" t="n">
-        <v>-1648353000</v>
+        <v>-1538642000</v>
       </c>
       <c r="BA3" t="n">
-        <v>3108446000</v>
+        <v>3147215000</v>
       </c>
       <c r="BB3" t="n">
-        <v>955139000</v>
+        <v>978351000</v>
       </c>
       <c r="BC3" t="inlineStr"/>
       <c r="BD3" t="n">
-        <v>1088770000</v>
+        <v>1102482000</v>
       </c>
       <c r="BE3" t="n">
-        <v>743268000</v>
+        <v>737724000</v>
       </c>
       <c r="BF3" t="n">
-        <v>321269000</v>
+        <v>328658000</v>
       </c>
       <c r="BG3" t="n">
         <v>0</v>
       </c>
       <c r="BH3" t="n">
-        <v>2344517000</v>
+        <v>5560598000</v>
       </c>
       <c r="BI3" t="n">
-        <v>113056000</v>
+        <v>217722000</v>
       </c>
       <c r="BJ3" t="n">
-        <v>16449000</v>
+        <v>33580000</v>
       </c>
       <c r="BK3" t="n">
-        <v>1118895000</v>
+        <v>722208000</v>
       </c>
       <c r="BL3" t="n">
-        <v>925538000</v>
+        <v>4358627000</v>
       </c>
       <c r="BM3" t="inlineStr"/>
       <c r="BN3" t="n">
-        <v>867704000</v>
+        <v>4293901000</v>
       </c>
       <c r="BO3" t="n">
-        <v>12205000</v>
+        <v>11083000</v>
       </c>
       <c r="BP3" t="n">
-        <v>45629000</v>
+        <v>53643000</v>
       </c>
       <c r="BQ3" t="n">
-        <v>0</v>
+        <v>5838000</v>
       </c>
       <c r="BR3" t="n">
-        <v>104432000</v>
+        <v>876446000</v>
       </c>
       <c r="BS3" t="n">
         <v>-105007000</v>
       </c>
       <c r="BT3" t="n">
-        <v>209439000</v>
+        <v>259245000</v>
       </c>
       <c r="BU3" t="n">
-        <v>66147000</v>
+        <v>68385000</v>
       </c>
       <c r="BV3" t="n">
-        <v>796000</v>
+        <v>8646000</v>
       </c>
       <c r="BW3" t="n">
-        <v>65351000</v>
+        <v>59739000</v>
       </c>
       <c r="BX3" t="n">
-        <v>65351000</v>
+        <v>59739000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44926</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
         <v>61543000</v>
@@ -2078,49 +2094,47 @@
         <v>61543000</v>
       </c>
       <c r="D4" t="n">
-        <v>6754384000</v>
+        <v>5001585000</v>
       </c>
       <c r="E4" t="n">
-        <v>6818021000</v>
+        <v>5075071000</v>
       </c>
       <c r="F4" t="n">
-        <v>-3695483000</v>
+        <v>-6350809000</v>
       </c>
       <c r="G4" t="n">
-        <v>3118640000</v>
+        <v>-1283873000</v>
       </c>
       <c r="H4" t="n">
-        <v>-8987107000</v>
+        <v>-9453660000</v>
       </c>
       <c r="I4" t="n">
-        <v>-3695483000</v>
+        <v>-6350809000</v>
       </c>
       <c r="J4" t="n">
-        <v>3898000</v>
+        <v>8135000</v>
       </c>
       <c r="K4" t="n">
-        <v>-3695483000</v>
+        <v>-6350809000</v>
       </c>
       <c r="L4" t="n">
-        <v>-3616272000</v>
+        <v>-6344800000</v>
       </c>
       <c r="M4" t="n">
-        <v>-3667098000</v>
+        <v>-6314233000</v>
       </c>
       <c r="N4" t="n">
-        <v>28385000</v>
+        <v>36576000</v>
       </c>
       <c r="O4" t="n">
-        <v>-3695483000</v>
+        <v>-6350809000</v>
       </c>
       <c r="P4" t="n">
-        <v>30001000</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>140000</v>
-      </c>
+        <v>29936000</v>
+      </c>
+      <c r="Q4" t="inlineStr"/>
       <c r="R4" t="n">
-        <v>-7499627000</v>
+        <v>-10178933000</v>
       </c>
       <c r="S4" t="n">
         <v>2557466000</v>
@@ -2132,83 +2146,83 @@
         <v>55983000</v>
       </c>
       <c r="V4" t="n">
-        <v>14772157000</v>
+        <v>11952189000</v>
       </c>
       <c r="W4" t="n">
-        <v>224452000</v>
+        <v>154012000</v>
       </c>
       <c r="X4" t="inlineStr"/>
       <c r="Y4" t="n">
-        <v>131656000</v>
+        <v>131486000</v>
       </c>
       <c r="Z4" t="n">
-        <v>11907000</v>
+        <v>11678000</v>
       </c>
       <c r="AA4" t="n">
-        <v>80889000</v>
+        <v>10848000</v>
       </c>
       <c r="AB4" t="n">
-        <v>1678000</v>
+        <v>4839000</v>
       </c>
       <c r="AC4" t="n">
-        <v>79211000</v>
+        <v>6009000</v>
       </c>
       <c r="AD4" t="n">
-        <v>14547705000</v>
+        <v>11798177000</v>
       </c>
       <c r="AE4" t="n">
-        <v>74518000</v>
+        <v>67255000</v>
       </c>
       <c r="AF4" t="n">
-        <v>6737132000</v>
+        <v>5064223000</v>
       </c>
       <c r="AG4" t="n">
-        <v>2220000</v>
+        <v>3296000</v>
       </c>
       <c r="AH4" t="n">
-        <v>6734912000</v>
+        <v>5060927000</v>
       </c>
       <c r="AI4" t="n">
-        <v>6179944000</v>
+        <v>6038290000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>5722404000</v>
+        <v>5629241000</v>
       </c>
       <c r="AK4" t="n">
-        <v>226086000</v>
+        <v>204059000</v>
       </c>
       <c r="AL4" t="n">
-        <v>231454000</v>
+        <v>204990000</v>
       </c>
       <c r="AM4" t="n">
-        <v>11105059000</v>
+        <v>5637956000</v>
       </c>
       <c r="AN4" t="n">
-        <v>5544461000</v>
+        <v>3293439000</v>
       </c>
       <c r="AO4" t="n">
         <v>3082000</v>
       </c>
       <c r="AP4" t="n">
-        <v>6072000</v>
+        <v>5662000</v>
       </c>
       <c r="AQ4" t="n">
-        <v>13220000</v>
+        <v>0</v>
       </c>
       <c r="AR4" t="n">
-        <v>13220000</v>
+        <v>0</v>
       </c>
       <c r="AS4" t="n">
-        <v>30638000</v>
+        <v>31067000</v>
       </c>
       <c r="AT4" t="n">
         <v>0</v>
       </c>
       <c r="AU4" t="n">
-        <v>30638000</v>
+        <v>31067000</v>
       </c>
       <c r="AV4" t="n">
-        <v>3869392000</v>
+        <v>1793535000</v>
       </c>
       <c r="AW4" t="n">
         <v>0</v>
@@ -2217,134 +2231,132 @@
         <v>0</v>
       </c>
       <c r="AY4" t="n">
-        <v>1608573000</v>
+        <v>1460093000</v>
       </c>
       <c r="AZ4" t="n">
-        <v>-1538642000</v>
+        <v>-1648353000</v>
       </c>
       <c r="BA4" t="n">
-        <v>3147215000</v>
+        <v>3108446000</v>
       </c>
       <c r="BB4" t="n">
-        <v>978351000</v>
+        <v>955139000</v>
       </c>
       <c r="BC4" t="inlineStr"/>
       <c r="BD4" t="n">
-        <v>1102482000</v>
+        <v>1088770000</v>
       </c>
       <c r="BE4" t="n">
-        <v>737724000</v>
+        <v>743268000</v>
       </c>
       <c r="BF4" t="n">
-        <v>328658000</v>
+        <v>321269000</v>
       </c>
       <c r="BG4" t="n">
         <v>0</v>
       </c>
       <c r="BH4" t="n">
-        <v>5560598000</v>
+        <v>2344517000</v>
       </c>
       <c r="BI4" t="n">
-        <v>217722000</v>
+        <v>113056000</v>
       </c>
       <c r="BJ4" t="n">
-        <v>33580000</v>
+        <v>16449000</v>
       </c>
       <c r="BK4" t="n">
-        <v>722208000</v>
+        <v>1118895000</v>
       </c>
       <c r="BL4" t="n">
-        <v>4358627000</v>
+        <v>925538000</v>
       </c>
       <c r="BM4" t="inlineStr"/>
       <c r="BN4" t="n">
-        <v>4293901000</v>
+        <v>867704000</v>
       </c>
       <c r="BO4" t="n">
-        <v>11083000</v>
+        <v>12205000</v>
       </c>
       <c r="BP4" t="n">
-        <v>53643000</v>
+        <v>45629000</v>
       </c>
       <c r="BQ4" t="n">
-        <v>5838000</v>
+        <v>0</v>
       </c>
       <c r="BR4" t="n">
-        <v>876446000</v>
+        <v>104432000</v>
       </c>
       <c r="BS4" t="n">
         <v>-105007000</v>
       </c>
       <c r="BT4" t="n">
-        <v>259245000</v>
+        <v>209439000</v>
       </c>
       <c r="BU4" t="n">
-        <v>68385000</v>
+        <v>66147000</v>
       </c>
       <c r="BV4" t="n">
-        <v>8646000</v>
+        <v>796000</v>
       </c>
       <c r="BW4" t="n">
-        <v>59739000</v>
+        <v>65351000</v>
       </c>
       <c r="BX4" t="n">
-        <v>59739000</v>
+        <v>65351000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44561</v>
+        <v>45657</v>
       </c>
       <c r="B5" t="n">
-        <v>61543000</v>
+        <v>61543075</v>
       </c>
       <c r="C5" t="n">
-        <v>61543000</v>
+        <v>61543075</v>
       </c>
       <c r="D5" t="n">
-        <v>10948747000</v>
+        <v>4978046000</v>
       </c>
       <c r="E5" t="n">
-        <v>11112752000</v>
+        <v>5017853000</v>
       </c>
       <c r="F5" t="n">
-        <v>-850618000</v>
+        <v>-7621857000</v>
       </c>
       <c r="G5" t="n">
-        <v>10250333000</v>
+        <v>-2607519000</v>
       </c>
       <c r="H5" t="n">
-        <v>-7416620000</v>
+        <v>-10241444000</v>
       </c>
       <c r="I5" t="n">
-        <v>-850618000</v>
+        <v>-7621857000</v>
       </c>
       <c r="J5" t="n">
-        <v>11801000</v>
+        <v>3515000</v>
       </c>
       <c r="K5" t="n">
-        <v>-850618000</v>
+        <v>-7621857000</v>
       </c>
       <c r="L5" t="n">
-        <v>-591011000</v>
+        <v>-7621857000</v>
       </c>
       <c r="M5" t="n">
-        <v>-844868000</v>
+        <v>-7586267000</v>
       </c>
       <c r="N5" t="n">
-        <v>5750000</v>
+        <v>35590000</v>
       </c>
       <c r="O5" t="n">
-        <v>-850618000</v>
+        <v>-7621857000</v>
       </c>
       <c r="P5" t="n">
-        <v>30185000</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>140000</v>
-      </c>
+        <v>29930000</v>
+      </c>
+      <c r="Q5" t="inlineStr"/>
       <c r="R5" t="n">
-        <v>-4628951000</v>
+        <v>-11442307000</v>
       </c>
       <c r="S5" t="n">
         <v>2557466000</v>
@@ -2356,85 +2368,79 @@
         <v>55983000</v>
       </c>
       <c r="V5" t="n">
-        <v>16580618000</v>
+        <v>12420778000</v>
       </c>
       <c r="W5" t="n">
-        <v>593919000</v>
-      </c>
-      <c r="X5" t="n">
-        <v>187560000</v>
-      </c>
+        <v>144178000</v>
+      </c>
+      <c r="X5" t="inlineStr"/>
       <c r="Y5" t="n">
-        <v>133858000</v>
+        <v>130852000</v>
       </c>
       <c r="Z5" t="n">
-        <v>12036000</v>
+        <v>11973000</v>
       </c>
       <c r="AA5" t="n">
-        <v>260465000</v>
+        <v>1353000</v>
       </c>
       <c r="AB5" t="n">
-        <v>858000</v>
+        <v>1353000</v>
       </c>
       <c r="AC5" t="n">
-        <v>259607000</v>
+        <v>0</v>
       </c>
       <c r="AD5" t="n">
-        <v>15986699000</v>
+        <v>12276600000</v>
       </c>
       <c r="AE5" t="n">
-        <v>74518000</v>
+        <v>64326000</v>
       </c>
       <c r="AF5" t="n">
-        <v>10852287000</v>
+        <v>5016500000</v>
       </c>
       <c r="AG5" t="n">
-        <v>10943000</v>
+        <v>2162000</v>
       </c>
       <c r="AH5" t="n">
-        <v>10841344000</v>
+        <v>5014338000</v>
       </c>
       <c r="AI5" t="n">
-        <v>3460756000</v>
+        <v>6527369000</v>
       </c>
       <c r="AJ5" t="n">
-        <v>2976487000</v>
+        <v>6118522000</v>
       </c>
       <c r="AK5" t="n">
-        <v>172002000</v>
+        <v>217628000</v>
       </c>
       <c r="AL5" t="n">
-        <v>312267000</v>
+        <v>191219000</v>
       </c>
       <c r="AM5" t="n">
-        <v>15735750000</v>
+        <v>4834511000</v>
       </c>
       <c r="AN5" t="n">
-        <v>7165671000</v>
+        <v>2799355000</v>
       </c>
       <c r="AO5" t="n">
-        <v>2824000</v>
+        <v>3139000</v>
       </c>
       <c r="AP5" t="n">
-        <v>7026000</v>
-      </c>
-      <c r="AQ5" t="n">
-        <v>23001000</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>23001000</v>
-      </c>
+        <v>5842000</v>
+      </c>
+      <c r="AQ5" t="inlineStr"/>
+      <c r="AR5" t="inlineStr"/>
       <c r="AS5" t="n">
-        <v>30246000</v>
+        <v>31217000</v>
       </c>
       <c r="AT5" t="n">
         <v>0</v>
       </c>
       <c r="AU5" t="n">
-        <v>30246000</v>
+        <v>31217000</v>
       </c>
       <c r="AV5" t="n">
-        <v>5075502000</v>
+        <v>1385836000</v>
       </c>
       <c r="AW5" t="n">
         <v>0</v>
@@ -2443,82 +2449,76 @@
         <v>0</v>
       </c>
       <c r="AY5" t="n">
-        <v>1973441000</v>
+        <v>1373321000</v>
       </c>
       <c r="AZ5" t="n">
-        <v>-1263490000</v>
+        <v>-1724370000</v>
       </c>
       <c r="BA5" t="n">
-        <v>3236931000</v>
+        <v>3097691000</v>
       </c>
       <c r="BB5" t="n">
-        <v>984248000</v>
-      </c>
-      <c r="BC5" t="n">
-        <v>1932482000</v>
-      </c>
+        <v>955379000</v>
+      </c>
+      <c r="BC5" t="inlineStr"/>
       <c r="BD5" t="n">
-        <v>1073341000</v>
+        <v>1089297000</v>
       </c>
       <c r="BE5" t="n">
-        <v>838704000</v>
+        <v>740290000</v>
       </c>
       <c r="BF5" t="n">
-        <v>340638000</v>
+        <v>312725000</v>
       </c>
       <c r="BG5" t="n">
         <v>0</v>
       </c>
       <c r="BH5" t="n">
-        <v>8570079000</v>
+        <v>2035156000</v>
       </c>
       <c r="BI5" t="n">
-        <v>59139000</v>
+        <v>106901000</v>
       </c>
       <c r="BJ5" t="n">
-        <v>18449000</v>
+        <v>15135000</v>
       </c>
       <c r="BK5" t="n">
-        <v>707571000</v>
+        <v>926618000</v>
       </c>
       <c r="BL5" t="n">
-        <v>7376317000</v>
-      </c>
-      <c r="BM5" t="n">
-        <v>285077000</v>
-      </c>
+        <v>844597000</v>
+      </c>
+      <c r="BM5" t="inlineStr"/>
       <c r="BN5" t="n">
-        <v>7298194000</v>
+        <v>804006000</v>
       </c>
       <c r="BO5" t="n">
-        <v>18817000</v>
+        <v>9076000</v>
       </c>
       <c r="BP5" t="n">
-        <v>59306000</v>
-      </c>
-      <c r="BQ5" t="n">
-        <v>5739000</v>
-      </c>
+        <v>31515000</v>
+      </c>
+      <c r="BQ5" t="inlineStr"/>
       <c r="BR5" t="n">
-        <v>945496000</v>
+        <v>105095000</v>
       </c>
       <c r="BS5" t="n">
-        <v>-52234000</v>
+        <v>-105040000</v>
       </c>
       <c r="BT5" t="n">
-        <v>290159000</v>
+        <v>210135000</v>
       </c>
       <c r="BU5" t="n">
-        <v>164939000</v>
+        <v>36810000</v>
       </c>
       <c r="BV5" t="n">
-        <v>12735000</v>
+        <v>518000</v>
       </c>
       <c r="BW5" t="n">
-        <v>152204000</v>
+        <v>36292000</v>
       </c>
       <c r="BX5" t="n">
-        <v>152204000</v>
+        <v>36292000</v>
       </c>
     </row>
   </sheetData>
@@ -2794,612 +2794,612 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
+        <v>44561</v>
       </c>
       <c r="B2" t="n">
-        <v>90476000</v>
+        <v>14405000</v>
       </c>
       <c r="C2" t="n">
-        <v>-67084000</v>
+        <v>-3044251000</v>
       </c>
       <c r="D2" t="n">
-        <v>5000000</v>
+        <v>2769814000</v>
       </c>
       <c r="E2" t="n">
-        <v>-3098000</v>
+        <v>-439486000</v>
       </c>
       <c r="F2" t="n">
-        <v>36292000</v>
+        <v>152204000</v>
       </c>
       <c r="G2" t="n">
-        <v>65351000</v>
+        <v>219083000</v>
       </c>
       <c r="H2" t="n">
-        <v>-558000</v>
+        <v>-5002000</v>
       </c>
       <c r="I2" t="n">
-        <v>-28501000</v>
+        <v>-61877000</v>
       </c>
       <c r="J2" t="n">
-        <v>-119885000</v>
+        <v>-158424000</v>
       </c>
       <c r="K2" t="n">
-        <v>168000</v>
+        <v>324318000</v>
       </c>
       <c r="L2" t="n">
-        <v>-54692000</v>
+        <v>-192000000</v>
       </c>
       <c r="M2" t="n">
-        <v>-62084000</v>
-      </c>
-      <c r="N2" t="n">
-        <v>-62084000</v>
-      </c>
-      <c r="O2" t="n">
-        <v>-67084000</v>
-      </c>
-      <c r="P2" t="n">
-        <v>5000000</v>
-      </c>
+        <v>-274437000</v>
+      </c>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr"/>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>-274437000</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S2" t="inlineStr"/>
+        <v>-3044251000</v>
+      </c>
+      <c r="S2" t="n">
+        <v>2769814000</v>
+      </c>
       <c r="T2" t="n">
-        <v>-2190000</v>
+        <v>-357344000</v>
       </c>
       <c r="U2" t="n">
-        <v>-494000</v>
+        <v>33373000</v>
       </c>
       <c r="V2" t="n">
-        <v>492000</v>
+        <v>2109000</v>
       </c>
       <c r="W2" t="n">
-        <v>231000</v>
+        <v>5340000</v>
       </c>
       <c r="X2" t="n">
-        <v>307000</v>
+        <v>18964000</v>
       </c>
       <c r="Y2" t="n">
-        <v>-76000</v>
+        <v>-13624000</v>
       </c>
       <c r="Z2" t="n">
-        <v>-355000</v>
+        <v>-66215000</v>
       </c>
       <c r="AA2" t="n">
         <v>0</v>
       </c>
       <c r="AB2" t="n">
-        <v>-355000</v>
+        <v>-66215000</v>
       </c>
       <c r="AC2" t="n">
-        <v>0</v>
+        <v>14654000</v>
       </c>
       <c r="AD2" t="n">
-        <v>0</v>
+        <v>14654000</v>
       </c>
       <c r="AE2" t="n">
         <v>0</v>
       </c>
       <c r="AF2" t="n">
-        <v>-2064000</v>
+        <v>-346605000</v>
       </c>
       <c r="AG2" t="n">
-        <v>1034000</v>
+        <v>92881000</v>
       </c>
       <c r="AH2" t="n">
-        <v>-3098000</v>
+        <v>-439486000</v>
       </c>
       <c r="AI2" t="n">
-        <v>93574000</v>
+        <v>453891000</v>
       </c>
       <c r="AJ2" t="n">
-        <v>-1289000</v>
-      </c>
-      <c r="AK2" t="inlineStr"/>
+        <v>-16279000</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>1297000</v>
+      </c>
       <c r="AL2" t="n">
-        <v>19000</v>
+        <v>1294000</v>
       </c>
       <c r="AM2" t="n">
-        <v>135944000</v>
+        <v>537230000</v>
       </c>
       <c r="AN2" t="n">
-        <v>36900000</v>
+        <v>-163566000</v>
       </c>
       <c r="AO2" t="n">
-        <v>2510000</v>
+        <v>345134000</v>
       </c>
       <c r="AP2" t="n">
-        <v>9875000</v>
+        <v>139912000</v>
       </c>
       <c r="AQ2" t="n">
-        <v>86659000</v>
+        <v>215750000</v>
       </c>
       <c r="AR2" t="n">
-        <v>553133000</v>
-      </c>
-      <c r="AS2" t="inlineStr"/>
+        <v>1138796000</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>21699000</v>
+      </c>
       <c r="AT2" t="n">
-        <v>80011000</v>
+        <v>120293000</v>
       </c>
       <c r="AU2" t="n">
-        <v>80011000</v>
+        <v>120293000</v>
       </c>
       <c r="AV2" t="n">
-        <v>408102000</v>
+        <v>376646000</v>
       </c>
       <c r="AW2" t="n">
-        <v>50000</v>
+        <v>-10000</v>
       </c>
       <c r="AX2" t="n">
-        <v>-1029000</v>
+        <v>-31363000</v>
       </c>
       <c r="AY2" t="n">
         <v>0</v>
       </c>
       <c r="AZ2" t="n">
-        <v>-1263326000</v>
+        <v>-1829267000</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45291</v>
+        <v>44926</v>
       </c>
       <c r="B3" t="n">
-        <v>686562000</v>
+        <v>-53239000</v>
       </c>
       <c r="C3" t="n">
-        <v>-1457663000</v>
+        <v>-66326000</v>
       </c>
       <c r="D3" t="n">
         <v>5000000</v>
       </c>
       <c r="E3" t="n">
-        <v>-2646000</v>
+        <v>-10761000</v>
       </c>
       <c r="F3" t="n">
-        <v>65351000</v>
+        <v>59739000</v>
       </c>
       <c r="G3" t="n">
-        <v>59739000</v>
+        <v>152204000</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>-26137000</v>
       </c>
       <c r="I3" t="n">
-        <v>5612000</v>
+        <v>-66328000</v>
       </c>
       <c r="J3" t="n">
-        <v>-1871150000</v>
+        <v>-115993000</v>
       </c>
       <c r="K3" t="n">
-        <v>119000</v>
+        <v>11391000</v>
       </c>
       <c r="L3" t="n">
-        <v>-412878000</v>
+        <v>-54261000</v>
       </c>
       <c r="M3" t="n">
-        <v>-1452663000</v>
+        <v>-61326000</v>
       </c>
       <c r="N3" t="n">
-        <v>-1447270000</v>
+        <v>-55743000</v>
       </c>
       <c r="O3" t="n">
-        <v>-1452270000</v>
+        <v>-60743000</v>
       </c>
       <c r="P3" t="n">
         <v>5000000</v>
       </c>
       <c r="Q3" t="n">
-        <v>-5393000</v>
+        <v>-5583000</v>
       </c>
       <c r="R3" t="n">
-        <v>-5393000</v>
-      </c>
-      <c r="S3" t="inlineStr"/>
+        <v>-5583000</v>
+      </c>
+      <c r="S3" t="n">
+        <v>5000000</v>
+      </c>
       <c r="T3" t="n">
-        <v>1187554000</v>
-      </c>
-      <c r="U3" t="inlineStr"/>
+        <v>92143000</v>
+      </c>
+      <c r="U3" t="n">
+        <v>10265000</v>
+      </c>
       <c r="V3" t="n">
-        <v>604000</v>
+        <v>681000</v>
       </c>
       <c r="W3" t="n">
-        <v>20449000</v>
+        <v>14833000</v>
       </c>
       <c r="X3" t="n">
-        <v>20449000</v>
+        <v>30554000</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>-15721000</v>
       </c>
       <c r="Z3" t="n">
-        <v>1165475000</v>
+        <v>-95813000</v>
       </c>
       <c r="AA3" t="n">
-        <v>1169100000</v>
+        <v>5748000</v>
       </c>
       <c r="AB3" t="n">
-        <v>-3625000</v>
+        <v>-101561000</v>
       </c>
       <c r="AC3" t="n">
-        <v>1253000</v>
+        <v>-34491000</v>
       </c>
       <c r="AD3" t="n">
-        <v>1296000</v>
+        <v>0</v>
       </c>
       <c r="AE3" t="n">
-        <v>-43000</v>
+        <v>-34491000</v>
       </c>
       <c r="AF3" t="n">
-        <v>-227000</v>
+        <v>196668000</v>
       </c>
       <c r="AG3" t="n">
-        <v>2419000</v>
+        <v>207429000</v>
       </c>
       <c r="AH3" t="n">
-        <v>-2646000</v>
+        <v>-10761000</v>
       </c>
       <c r="AI3" t="n">
-        <v>689208000</v>
+        <v>-42478000</v>
       </c>
       <c r="AJ3" t="n">
-        <v>28177000</v>
-      </c>
-      <c r="AK3" t="inlineStr"/>
+        <v>-5214000</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>0</v>
+      </c>
       <c r="AL3" t="n">
-        <v>104000</v>
+        <v>752000</v>
       </c>
       <c r="AM3" t="n">
-        <v>660857000</v>
+        <v>-1042000</v>
       </c>
       <c r="AN3" t="n">
-        <v>-504224000</v>
+        <v>112827000</v>
       </c>
       <c r="AO3" t="n">
-        <v>687670000</v>
+        <v>-56359000</v>
       </c>
       <c r="AP3" t="n">
-        <v>1533761000</v>
+        <v>-10365000</v>
       </c>
       <c r="AQ3" t="n">
-        <v>-1056350000</v>
+        <v>-47145000</v>
       </c>
       <c r="AR3" t="n">
-        <v>871145000</v>
+        <v>1302652000</v>
       </c>
       <c r="AS3" t="inlineStr"/>
       <c r="AT3" t="n">
-        <v>88884000</v>
+        <v>106845000</v>
       </c>
       <c r="AU3" t="n">
-        <v>88884000</v>
+        <v>106845000</v>
       </c>
       <c r="AV3" t="n">
-        <v>910516000</v>
+        <v>1188471000</v>
       </c>
       <c r="AW3" t="n">
-        <v>82000</v>
+        <v>0</v>
       </c>
       <c r="AX3" t="n">
-        <v>-72000</v>
+        <v>-192784000</v>
       </c>
       <c r="AY3" t="n">
-        <v>13716000</v>
+        <v>-410978000</v>
       </c>
       <c r="AZ3" t="n">
-        <v>-2698806000</v>
+        <v>-2805223000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44926</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
-        <v>-53239000</v>
+        <v>686562000</v>
       </c>
       <c r="C4" t="n">
-        <v>-66326000</v>
+        <v>-1457663000</v>
       </c>
       <c r="D4" t="n">
         <v>5000000</v>
       </c>
       <c r="E4" t="n">
-        <v>-10761000</v>
+        <v>-2646000</v>
       </c>
       <c r="F4" t="n">
+        <v>65351000</v>
+      </c>
+      <c r="G4" t="n">
         <v>59739000</v>
       </c>
-      <c r="G4" t="n">
-        <v>152204000</v>
-      </c>
       <c r="H4" t="n">
-        <v>-26137000</v>
+        <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>-66328000</v>
+        <v>5612000</v>
       </c>
       <c r="J4" t="n">
-        <v>-115993000</v>
+        <v>-1871150000</v>
       </c>
       <c r="K4" t="n">
-        <v>11391000</v>
+        <v>119000</v>
       </c>
       <c r="L4" t="n">
-        <v>-54261000</v>
+        <v>-412878000</v>
       </c>
       <c r="M4" t="n">
-        <v>-61326000</v>
+        <v>-1452663000</v>
       </c>
       <c r="N4" t="n">
-        <v>-55743000</v>
+        <v>-1447270000</v>
       </c>
       <c r="O4" t="n">
-        <v>-60743000</v>
+        <v>-1452270000</v>
       </c>
       <c r="P4" t="n">
         <v>5000000</v>
       </c>
       <c r="Q4" t="n">
-        <v>-5583000</v>
+        <v>-5393000</v>
       </c>
       <c r="R4" t="n">
-        <v>-5583000</v>
-      </c>
-      <c r="S4" t="n">
-        <v>5000000</v>
-      </c>
+        <v>-5393000</v>
+      </c>
+      <c r="S4" t="inlineStr"/>
       <c r="T4" t="n">
-        <v>92143000</v>
-      </c>
-      <c r="U4" t="n">
-        <v>10265000</v>
-      </c>
+        <v>1187554000</v>
+      </c>
+      <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>681000</v>
+        <v>604000</v>
       </c>
       <c r="W4" t="n">
-        <v>14833000</v>
+        <v>20449000</v>
       </c>
       <c r="X4" t="n">
-        <v>30554000</v>
+        <v>20449000</v>
       </c>
       <c r="Y4" t="n">
-        <v>-15721000</v>
+        <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>-95813000</v>
+        <v>1165475000</v>
       </c>
       <c r="AA4" t="n">
-        <v>5748000</v>
+        <v>1169100000</v>
       </c>
       <c r="AB4" t="n">
-        <v>-101561000</v>
+        <v>-3625000</v>
       </c>
       <c r="AC4" t="n">
-        <v>-34491000</v>
+        <v>1253000</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>1296000</v>
       </c>
       <c r="AE4" t="n">
-        <v>-34491000</v>
+        <v>-43000</v>
       </c>
       <c r="AF4" t="n">
-        <v>196668000</v>
+        <v>-227000</v>
       </c>
       <c r="AG4" t="n">
-        <v>207429000</v>
+        <v>2419000</v>
       </c>
       <c r="AH4" t="n">
-        <v>-10761000</v>
+        <v>-2646000</v>
       </c>
       <c r="AI4" t="n">
-        <v>-42478000</v>
+        <v>689208000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>-5214000</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>0</v>
-      </c>
+        <v>28177000</v>
+      </c>
+      <c r="AK4" t="inlineStr"/>
       <c r="AL4" t="n">
-        <v>752000</v>
+        <v>104000</v>
       </c>
       <c r="AM4" t="n">
-        <v>-1042000</v>
+        <v>660857000</v>
       </c>
       <c r="AN4" t="n">
-        <v>112827000</v>
+        <v>-504224000</v>
       </c>
       <c r="AO4" t="n">
-        <v>-56359000</v>
+        <v>687670000</v>
       </c>
       <c r="AP4" t="n">
-        <v>-10365000</v>
+        <v>1533761000</v>
       </c>
       <c r="AQ4" t="n">
-        <v>-47145000</v>
+        <v>-1056350000</v>
       </c>
       <c r="AR4" t="n">
-        <v>1302652000</v>
+        <v>871145000</v>
       </c>
       <c r="AS4" t="inlineStr"/>
       <c r="AT4" t="n">
-        <v>106845000</v>
+        <v>88884000</v>
       </c>
       <c r="AU4" t="n">
-        <v>106845000</v>
+        <v>88884000</v>
       </c>
       <c r="AV4" t="n">
-        <v>1188471000</v>
+        <v>910516000</v>
       </c>
       <c r="AW4" t="n">
-        <v>0</v>
+        <v>82000</v>
       </c>
       <c r="AX4" t="n">
-        <v>-192784000</v>
+        <v>-72000</v>
       </c>
       <c r="AY4" t="n">
-        <v>-410978000</v>
+        <v>13716000</v>
       </c>
       <c r="AZ4" t="n">
-        <v>-2805223000</v>
+        <v>-2698806000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44561</v>
+        <v>45657</v>
       </c>
       <c r="B5" t="n">
-        <v>14405000</v>
+        <v>90476000</v>
       </c>
       <c r="C5" t="n">
-        <v>-3044251000</v>
+        <v>-67084000</v>
       </c>
       <c r="D5" t="n">
-        <v>2769814000</v>
+        <v>5000000</v>
       </c>
       <c r="E5" t="n">
-        <v>-439486000</v>
+        <v>-3098000</v>
       </c>
       <c r="F5" t="n">
-        <v>152204000</v>
+        <v>36292000</v>
       </c>
       <c r="G5" t="n">
-        <v>219083000</v>
+        <v>65351000</v>
       </c>
       <c r="H5" t="n">
-        <v>-5002000</v>
+        <v>-558000</v>
       </c>
       <c r="I5" t="n">
-        <v>-61877000</v>
+        <v>-28501000</v>
       </c>
       <c r="J5" t="n">
-        <v>-158424000</v>
+        <v>-119885000</v>
       </c>
       <c r="K5" t="n">
-        <v>324318000</v>
+        <v>168000</v>
       </c>
       <c r="L5" t="n">
-        <v>-192000000</v>
+        <v>-54692000</v>
       </c>
       <c r="M5" t="n">
-        <v>-274437000</v>
-      </c>
-      <c r="N5" t="inlineStr"/>
-      <c r="O5" t="inlineStr"/>
-      <c r="P5" t="inlineStr"/>
+        <v>-62084000</v>
+      </c>
+      <c r="N5" t="n">
+        <v>-62084000</v>
+      </c>
+      <c r="O5" t="n">
+        <v>-67084000</v>
+      </c>
+      <c r="P5" t="n">
+        <v>5000000</v>
+      </c>
       <c r="Q5" t="n">
-        <v>-274437000</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>-3044251000</v>
-      </c>
-      <c r="S5" t="n">
-        <v>2769814000</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="S5" t="inlineStr"/>
       <c r="T5" t="n">
-        <v>-357344000</v>
+        <v>-2190000</v>
       </c>
       <c r="U5" t="n">
-        <v>33373000</v>
+        <v>-494000</v>
       </c>
       <c r="V5" t="n">
-        <v>2109000</v>
+        <v>492000</v>
       </c>
       <c r="W5" t="n">
-        <v>5340000</v>
+        <v>231000</v>
       </c>
       <c r="X5" t="n">
-        <v>18964000</v>
+        <v>307000</v>
       </c>
       <c r="Y5" t="n">
-        <v>-13624000</v>
+        <v>-76000</v>
       </c>
       <c r="Z5" t="n">
-        <v>-66215000</v>
+        <v>-355000</v>
       </c>
       <c r="AA5" t="n">
         <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>-66215000</v>
+        <v>-355000</v>
       </c>
       <c r="AC5" t="n">
-        <v>14654000</v>
+        <v>0</v>
       </c>
       <c r="AD5" t="n">
-        <v>14654000</v>
+        <v>0</v>
       </c>
       <c r="AE5" t="n">
         <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>-346605000</v>
+        <v>-2064000</v>
       </c>
       <c r="AG5" t="n">
-        <v>92881000</v>
+        <v>1034000</v>
       </c>
       <c r="AH5" t="n">
-        <v>-439486000</v>
+        <v>-3098000</v>
       </c>
       <c r="AI5" t="n">
-        <v>453891000</v>
+        <v>93574000</v>
       </c>
       <c r="AJ5" t="n">
-        <v>-16279000</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>1297000</v>
-      </c>
+        <v>-1289000</v>
+      </c>
+      <c r="AK5" t="inlineStr"/>
       <c r="AL5" t="n">
-        <v>1294000</v>
+        <v>19000</v>
       </c>
       <c r="AM5" t="n">
-        <v>537230000</v>
+        <v>135944000</v>
       </c>
       <c r="AN5" t="n">
-        <v>-163566000</v>
+        <v>36900000</v>
       </c>
       <c r="AO5" t="n">
-        <v>345134000</v>
+        <v>2510000</v>
       </c>
       <c r="AP5" t="n">
-        <v>139912000</v>
+        <v>9875000</v>
       </c>
       <c r="AQ5" t="n">
-        <v>215750000</v>
+        <v>86659000</v>
       </c>
       <c r="AR5" t="n">
-        <v>1138796000</v>
-      </c>
-      <c r="AS5" t="n">
-        <v>21699000</v>
-      </c>
+        <v>553133000</v>
+      </c>
+      <c r="AS5" t="inlineStr"/>
       <c r="AT5" t="n">
-        <v>120293000</v>
+        <v>80011000</v>
       </c>
       <c r="AU5" t="n">
-        <v>120293000</v>
+        <v>80011000</v>
       </c>
       <c r="AV5" t="n">
-        <v>376646000</v>
+        <v>408102000</v>
       </c>
       <c r="AW5" t="n">
-        <v>-10000</v>
+        <v>50000</v>
       </c>
       <c r="AX5" t="n">
-        <v>-31363000</v>
+        <v>-1029000</v>
       </c>
       <c r="AY5" t="n">
         <v>0</v>
       </c>
       <c r="AZ5" t="n">
-        <v>-1829267000</v>
+        <v>-1263326000</v>
       </c>
     </row>
   </sheetData>
@@ -3924,192 +3924,192 @@
       </c>
       <c r="CX1" t="inlineStr">
         <is>
+          <t>corporateActions</t>
+        </is>
+      </c>
+      <c r="CY1" t="inlineStr">
+        <is>
+          <t>regularMarketTime</t>
+        </is>
+      </c>
+      <c r="CZ1" t="inlineStr">
+        <is>
+          <t>exchange</t>
+        </is>
+      </c>
+      <c r="DA1" t="inlineStr">
+        <is>
+          <t>messageBoardId</t>
+        </is>
+      </c>
+      <c r="DB1" t="inlineStr">
+        <is>
+          <t>exchangeTimezoneName</t>
+        </is>
+      </c>
+      <c r="DC1" t="inlineStr">
+        <is>
+          <t>exchangeTimezoneShortName</t>
+        </is>
+      </c>
+      <c r="DD1" t="inlineStr">
+        <is>
+          <t>gmtOffSetMilliseconds</t>
+        </is>
+      </c>
+      <c r="DE1" t="inlineStr">
+        <is>
+          <t>market</t>
+        </is>
+      </c>
+      <c r="DF1" t="inlineStr">
+        <is>
+          <t>esgPopulated</t>
+        </is>
+      </c>
+      <c r="DG1" t="inlineStr">
+        <is>
+          <t>longName</t>
+        </is>
+      </c>
+      <c r="DH1" t="inlineStr">
+        <is>
+          <t>shortName</t>
+        </is>
+      </c>
+      <c r="DI1" t="inlineStr">
+        <is>
+          <t>hasPrePostMarketData</t>
+        </is>
+      </c>
+      <c r="DJ1" t="inlineStr">
+        <is>
+          <t>firstTradeDateMilliseconds</t>
+        </is>
+      </c>
+      <c r="DK1" t="inlineStr">
+        <is>
+          <t>regularMarketChange</t>
+        </is>
+      </c>
+      <c r="DL1" t="inlineStr">
+        <is>
+          <t>regularMarketDayRange</t>
+        </is>
+      </c>
+      <c r="DM1" t="inlineStr">
+        <is>
+          <t>fullExchangeName</t>
+        </is>
+      </c>
+      <c r="DN1" t="inlineStr">
+        <is>
+          <t>averageDailyVolume3Month</t>
+        </is>
+      </c>
+      <c r="DO1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekLowChange</t>
+        </is>
+      </c>
+      <c r="DP1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekLowChangePercent</t>
+        </is>
+      </c>
+      <c r="DQ1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekRange</t>
+        </is>
+      </c>
+      <c r="DR1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekHighChange</t>
+        </is>
+      </c>
+      <c r="DS1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekHighChangePercent</t>
+        </is>
+      </c>
+      <c r="DT1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekChangePercent</t>
+        </is>
+      </c>
+      <c r="DU1" t="inlineStr">
+        <is>
+          <t>earningsTimestampStart</t>
+        </is>
+      </c>
+      <c r="DV1" t="inlineStr">
+        <is>
+          <t>earningsTimestampEnd</t>
+        </is>
+      </c>
+      <c r="DW1" t="inlineStr">
+        <is>
+          <t>isEarningsDateEstimate</t>
+        </is>
+      </c>
+      <c r="DX1" t="inlineStr">
+        <is>
+          <t>epsTrailingTwelveMonths</t>
+        </is>
+      </c>
+      <c r="DY1" t="inlineStr">
+        <is>
+          <t>marketState</t>
+        </is>
+      </c>
+      <c r="DZ1" t="inlineStr">
+        <is>
           <t>fiftyDayAverageChange</t>
         </is>
       </c>
-      <c r="CY1" t="inlineStr">
+      <c r="EA1" t="inlineStr">
         <is>
           <t>fiftyDayAverageChangePercent</t>
         </is>
       </c>
-      <c r="CZ1" t="inlineStr">
+      <c r="EB1" t="inlineStr">
         <is>
           <t>twoHundredDayAverageChange</t>
         </is>
       </c>
-      <c r="DA1" t="inlineStr">
+      <c r="EC1" t="inlineStr">
         <is>
           <t>twoHundredDayAverageChangePercent</t>
         </is>
       </c>
-      <c r="DB1" t="inlineStr">
+      <c r="ED1" t="inlineStr">
         <is>
           <t>priceToBook</t>
         </is>
       </c>
-      <c r="DC1" t="inlineStr">
+      <c r="EE1" t="inlineStr">
         <is>
           <t>sourceInterval</t>
         </is>
       </c>
-      <c r="DD1" t="inlineStr">
+      <c r="EF1" t="inlineStr">
         <is>
           <t>exchangeDataDelayedBy</t>
         </is>
       </c>
-      <c r="DE1" t="inlineStr">
+      <c r="EG1" t="inlineStr">
         <is>
           <t>cryptoTradeable</t>
         </is>
       </c>
-      <c r="DF1" t="inlineStr">
-        <is>
-          <t>shortName</t>
-        </is>
-      </c>
-      <c r="DG1" t="inlineStr">
-        <is>
-          <t>longName</t>
-        </is>
-      </c>
-      <c r="DH1" t="inlineStr">
+      <c r="EH1" t="inlineStr">
         <is>
           <t>regularMarketChangePercent</t>
         </is>
       </c>
-      <c r="DI1" t="inlineStr">
+      <c r="EI1" t="inlineStr">
         <is>
           <t>regularMarketPrice</t>
-        </is>
-      </c>
-      <c r="DJ1" t="inlineStr">
-        <is>
-          <t>messageBoardId</t>
-        </is>
-      </c>
-      <c r="DK1" t="inlineStr">
-        <is>
-          <t>exchangeTimezoneName</t>
-        </is>
-      </c>
-      <c r="DL1" t="inlineStr">
-        <is>
-          <t>exchangeTimezoneShortName</t>
-        </is>
-      </c>
-      <c r="DM1" t="inlineStr">
-        <is>
-          <t>gmtOffSetMilliseconds</t>
-        </is>
-      </c>
-      <c r="DN1" t="inlineStr">
-        <is>
-          <t>market</t>
-        </is>
-      </c>
-      <c r="DO1" t="inlineStr">
-        <is>
-          <t>esgPopulated</t>
-        </is>
-      </c>
-      <c r="DP1" t="inlineStr">
-        <is>
-          <t>corporateActions</t>
-        </is>
-      </c>
-      <c r="DQ1" t="inlineStr">
-        <is>
-          <t>regularMarketTime</t>
-        </is>
-      </c>
-      <c r="DR1" t="inlineStr">
-        <is>
-          <t>exchange</t>
-        </is>
-      </c>
-      <c r="DS1" t="inlineStr">
-        <is>
-          <t>marketState</t>
-        </is>
-      </c>
-      <c r="DT1" t="inlineStr">
-        <is>
-          <t>hasPrePostMarketData</t>
-        </is>
-      </c>
-      <c r="DU1" t="inlineStr">
-        <is>
-          <t>firstTradeDateMilliseconds</t>
-        </is>
-      </c>
-      <c r="DV1" t="inlineStr">
-        <is>
-          <t>regularMarketChange</t>
-        </is>
-      </c>
-      <c r="DW1" t="inlineStr">
-        <is>
-          <t>regularMarketDayRange</t>
-        </is>
-      </c>
-      <c r="DX1" t="inlineStr">
-        <is>
-          <t>fullExchangeName</t>
-        </is>
-      </c>
-      <c r="DY1" t="inlineStr">
-        <is>
-          <t>averageDailyVolume3Month</t>
-        </is>
-      </c>
-      <c r="DZ1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekLowChange</t>
-        </is>
-      </c>
-      <c r="EA1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekLowChangePercent</t>
-        </is>
-      </c>
-      <c r="EB1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekRange</t>
-        </is>
-      </c>
-      <c r="EC1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekHighChange</t>
-        </is>
-      </c>
-      <c r="ED1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekHighChangePercent</t>
-        </is>
-      </c>
-      <c r="EE1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekChangePercent</t>
-        </is>
-      </c>
-      <c r="EF1" t="inlineStr">
-        <is>
-          <t>earningsTimestampStart</t>
-        </is>
-      </c>
-      <c r="EG1" t="inlineStr">
-        <is>
-          <t>earningsTimestampEnd</t>
-        </is>
-      </c>
-      <c r="EH1" t="inlineStr">
-        <is>
-          <t>isEarningsDateEstimate</t>
-        </is>
-      </c>
-      <c r="EI1" t="inlineStr">
-        <is>
-          <t>epsTrailingTwelveMonths</t>
         </is>
       </c>
       <c r="EJ1" t="inlineStr">
@@ -4151,7 +4151,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.chinahuajungroup.com</t>
+          <t>https://chinahuajungroup.com</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -4186,7 +4186,7 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>China Huajun Group Limited, an investment holding company, engages in printing, trading and logistics, and property development and investments businesses in the People's Republic of China, the United States, European countries, Hong Kong, and internationally. It manufactures and sells multi-colour packaging products, carton boxes, books, brochures, and other paper products. The company also engages in the distribution and sales of petrochemical products; provision of logistics and supply chain management services; marketing, cargo freight, and management services; and asset management, investment consulting, corporate finance, mergers and acquisitions, financial leasing, account receivable factoring, and other financial services. In addition, it engages in warehousing and transportation, and rubber activities; trades petrochemicals products; produces and sells photovoltaics products, monocrystalline silicon, solar stent, and related products; and provides processing services. Further, the company engages in property development and sales, property leasing and management, and various real estate business; technology development; and sales of chemical products. Additionally, it manufactures and maintains hydraulic machinery; produces and distributes paper products and surgical masks; and solar photovoltaic business. The company was formerly known as Huajun International Group Limited and changed its name to China Huajun Group Limited in October 2020. The company was incorporated in 1993 and is headquartered in Sheung Wan, Hong Kong. China Huajun Group Limited operates as a subsidiary of Huajun Group Limited.</t>
+          <t>China Huajun Group Limited, an investment holding company, engages in printing, trading and logistics, and property development and investments businesses in the People's Republic of China, the United States, European countries, Hong Kong, and internationally. It manufactures and sells multi-colour packaging products, carton boxes, books, brochures, and other paper products. The company also engages in the distribution and sales of petrochemical products; provision of logistics and supply chain management services; marketing, cargo freight, and management services; and asset management, investment consulting, corporate finance, mergers and acquisitions, financial leasing, account receivable factoring, and other financial services. In addition, it engages in warehousing and transportation, and rubber activities; trades petrochemicals products; produces and sells photovoltaics products, monocrystalline silicon, solar stent, and related products; and provides processing services. Further, the company engages in property development and sales, property leasing and management, and various real estate business; technology development; and sales of chemical products. Additionally, it produces and distributes paper products and surgical masks; solar photovoltaic business; and provision of hotel services. The company was formerly known as Huajun International Group Limited and changed its name to China Huajun Group Limited in October 2020. The company was incorporated in 1993 and is headquartered in Sheung Wan, Hong Kong. China Huajun Group Limited operates as a subsidiary of Huajun Group Limited.</t>
         </is>
       </c>
       <c r="O2" t="n">
@@ -4194,7 +4194,7 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>[{'maxAge': 1, 'name': 'Mr. Ruijie  Yan', 'age': 39, 'title': 'Executive Chairman &amp; CEO', 'yearBorn': 1986, 'fiscalYear': 2025, 'totalPay': 807225, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Ms. Yun  Chen', 'age': 41, 'title': 'Executive Director', 'yearBorn': 1984, 'fiscalYear': 2025, 'totalPay': 646243, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Ms. Xiaomei  Wang', 'age': 49, 'title': 'Executive Director', 'yearBorn': 1976, 'fiscalYear': 2025, 'totalPay': 138977, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Dr. Dayi  Li', 'age': 46, 'title': 'Executive Director', 'yearBorn': 1979, 'fiscalYear': 2025, 'totalPay': 138977, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Ka Lung  Tam', 'age': 45, 'title': 'CFO &amp; Company Secretary', 'yearBorn': 1980, 'fiscalYear': 2025, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Ms. Limin  Bao', 'age': 47, 'title': 'Chief Risk Officer &amp; Chief Compliance Officer', 'yearBorn': 1978, 'fiscalYear': 2025, 'totalPay': 85702, 'exercisedValue': 0, 'unexercisedValue': 0}]</t>
+          <t>[{'maxAge': 1, 'name': 'Mr. Ruijie  Yan', 'age': 39, 'title': 'Executive Chairman &amp; CEO', 'yearBorn': 1986, 'fiscalYear': 2025, 'totalPay': 806790, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Ms. Yun  Chen', 'age': 41, 'title': 'Executive Director', 'yearBorn': 1984, 'fiscalYear': 2025, 'totalPay': 645895, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Ms. Xiaomei  Wang', 'age': 49, 'title': 'Executive Director', 'yearBorn': 1976, 'fiscalYear': 2025, 'totalPay': 138902, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Dr. Dayi  Li', 'age': 46, 'title': 'Executive Director', 'yearBorn': 1979, 'fiscalYear': 2025, 'totalPay': 138902, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Ka Lung  Tam', 'age': 45, 'title': 'CFO &amp; Company Secretary', 'yearBorn': 1980, 'fiscalYear': 2025, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Ms. Limin  Bao', 'age': 47, 'title': 'Chief Risk Officer &amp; Chief Compliance Officer', 'yearBorn': 1978, 'fiscalYear': 2025, 'totalPay': 85656, 'exercisedValue': 0, 'unexercisedValue': 0}]</t>
         </is>
       </c>
       <c r="Q2" t="n">
@@ -4212,28 +4212,28 @@
         <v>3</v>
       </c>
       <c r="U2" t="n">
-        <v>1.28</v>
+        <v>1.38</v>
       </c>
       <c r="V2" t="n">
-        <v>1.28</v>
+        <v>1.38</v>
       </c>
       <c r="W2" t="n">
-        <v>1.26</v>
+        <v>1.38</v>
       </c>
       <c r="X2" t="n">
-        <v>1.28</v>
+        <v>1.39</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.28</v>
+        <v>1.38</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.28</v>
+        <v>1.38</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.26</v>
+        <v>1.38</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.28</v>
+        <v>1.39</v>
       </c>
       <c r="AC2" t="n">
         <v>1440115200</v>
@@ -4242,28 +4242,28 @@
         <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>-1.718</v>
+        <v>-1.677</v>
       </c>
       <c r="AF2" t="n">
-        <v>1080</v>
+        <v>4000</v>
       </c>
       <c r="AG2" t="n">
-        <v>1080</v>
+        <v>4000</v>
       </c>
       <c r="AH2" t="n">
-        <v>7502</v>
+        <v>7637</v>
       </c>
       <c r="AI2" t="n">
-        <v>108</v>
+        <v>400</v>
       </c>
       <c r="AJ2" t="n">
-        <v>108</v>
+        <v>400</v>
       </c>
       <c r="AK2" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AL2" t="n">
-        <v>1.38</v>
+        <v>1.28</v>
       </c>
       <c r="AM2" t="n">
         <v>0</v>
@@ -4275,10 +4275,10 @@
         <v>78775136</v>
       </c>
       <c r="AP2" t="n">
-        <v>78775136</v>
+        <v>84929443</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0.63</v>
+        <v>0.66</v>
       </c>
       <c r="AR2" t="n">
         <v>1.68</v>
@@ -4293,10 +4293,10 @@
         <v>0.057764675</v>
       </c>
       <c r="AV2" t="n">
-        <v>1.1116</v>
+        <v>1.2224</v>
       </c>
       <c r="AW2" t="n">
-        <v>1.08765</v>
+        <v>1.08685</v>
       </c>
       <c r="AX2" t="n">
         <v>0</v>
@@ -4334,7 +4334,7 @@
         <v>61543075</v>
       </c>
       <c r="BI2" t="n">
-        <v>-147.04115</v>
+        <v>-146.96313</v>
       </c>
       <c r="BJ2" t="n">
         <v>1767139200</v>
@@ -4366,10 +4366,10 @@
         <v>-12.214</v>
       </c>
       <c r="BS2" t="n">
-        <v>0.75342464</v>
+        <v>0.27999997</v>
       </c>
       <c r="BT2" t="n">
-        <v>0.27294624</v>
+        <v>0.24487448</v>
       </c>
       <c r="BU2" t="n">
         <v>2.48</v>
@@ -4476,143 +4476,143 @@
           <t>LOW</t>
         </is>
       </c>
-      <c r="CX2" t="n">
-        <v>0.16839993</v>
+      <c r="CX2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="CY2" t="n">
-        <v>0.15149328</v>
-      </c>
-      <c r="CZ2" t="n">
-        <v>0.19235003</v>
-      </c>
-      <c r="DA2" t="n">
-        <v>0.1768492</v>
-      </c>
-      <c r="DB2" t="n">
-        <v>-0.008705045999999999</v>
-      </c>
-      <c r="DC2" t="n">
+        <v>1780645960</v>
+      </c>
+      <c r="CZ2" t="inlineStr">
+        <is>
+          <t>HKG</t>
+        </is>
+      </c>
+      <c r="DA2" t="inlineStr">
+        <is>
+          <t>finmb_6497391</t>
+        </is>
+      </c>
+      <c r="DB2" t="inlineStr">
+        <is>
+          <t>Asia/Hong_Kong</t>
+        </is>
+      </c>
+      <c r="DC2" t="inlineStr">
+        <is>
+          <t>HKT</t>
+        </is>
+      </c>
+      <c r="DD2" t="n">
+        <v>28800000</v>
+      </c>
+      <c r="DE2" t="inlineStr">
+        <is>
+          <t>hk_market</t>
+        </is>
+      </c>
+      <c r="DF2" t="b">
+        <v>0</v>
+      </c>
+      <c r="DG2" t="inlineStr">
+        <is>
+          <t>China Huajun Group Limited</t>
+        </is>
+      </c>
+      <c r="DH2" t="inlineStr">
+        <is>
+          <t>CHINA HUAJUN GP</t>
+        </is>
+      </c>
+      <c r="DI2" t="b">
+        <v>0</v>
+      </c>
+      <c r="DJ2" t="n">
+        <v>946949400000</v>
+      </c>
+      <c r="DK2" t="n">
+        <v>-0.100000024</v>
+      </c>
+      <c r="DL2" t="inlineStr">
+        <is>
+          <t>1.38 - 1.39</t>
+        </is>
+      </c>
+      <c r="DM2" t="inlineStr">
+        <is>
+          <t>HKSE</t>
+        </is>
+      </c>
+      <c r="DN2" t="n">
+        <v>7637</v>
+      </c>
+      <c r="DO2" t="n">
+        <v>0.61999995</v>
+      </c>
+      <c r="DP2" t="n">
+        <v>0.9393937999999999</v>
+      </c>
+      <c r="DQ2" t="inlineStr">
+        <is>
+          <t>0.66 - 1.68</t>
+        </is>
+      </c>
+      <c r="DR2" t="n">
+        <v>-0.39999998</v>
+      </c>
+      <c r="DS2" t="n">
+        <v>-0.23809522</v>
+      </c>
+      <c r="DT2" t="n">
+        <v>27.999996</v>
+      </c>
+      <c r="DU2" t="n">
+        <v>1743421498</v>
+      </c>
+      <c r="DV2" t="n">
+        <v>1743421498</v>
+      </c>
+      <c r="DW2" t="b">
+        <v>0</v>
+      </c>
+      <c r="DX2" t="n">
+        <v>-4.4</v>
+      </c>
+      <c r="DY2" t="inlineStr">
+        <is>
+          <t>PREPRE</t>
+        </is>
+      </c>
+      <c r="DZ2" t="n">
+        <v>0.05760002</v>
+      </c>
+      <c r="EA2" t="n">
+        <v>0.047120437</v>
+      </c>
+      <c r="EB2" t="n">
+        <v>0.19314992</v>
+      </c>
+      <c r="EC2" t="n">
+        <v>0.17771533</v>
+      </c>
+      <c r="ED2" t="n">
+        <v>-0.008709667000000001</v>
+      </c>
+      <c r="EE2" t="n">
         <v>15</v>
       </c>
-      <c r="DD2" t="n">
+      <c r="EF2" t="n">
         <v>15</v>
       </c>
-      <c r="DE2" t="b">
-        <v>0</v>
-      </c>
-      <c r="DF2" t="inlineStr">
-        <is>
-          <t>CHINA HUAJUN GP</t>
-        </is>
-      </c>
-      <c r="DG2" t="inlineStr">
-        <is>
-          <t>China Huajun Group Limited</t>
-        </is>
-      </c>
-      <c r="DH2" t="n">
-        <v>0</v>
-      </c>
-      <c r="DI2" t="n">
+      <c r="EG2" t="b">
+        <v>0</v>
+      </c>
+      <c r="EH2" t="n">
+        <v>-7.246379</v>
+      </c>
+      <c r="EI2" t="n">
         <v>1.28</v>
-      </c>
-      <c r="DJ2" t="inlineStr">
-        <is>
-          <t>finmb_6497391</t>
-        </is>
-      </c>
-      <c r="DK2" t="inlineStr">
-        <is>
-          <t>Asia/Hong_Kong</t>
-        </is>
-      </c>
-      <c r="DL2" t="inlineStr">
-        <is>
-          <t>HKT</t>
-        </is>
-      </c>
-      <c r="DM2" t="n">
-        <v>28800000</v>
-      </c>
-      <c r="DN2" t="inlineStr">
-        <is>
-          <t>hk_market</t>
-        </is>
-      </c>
-      <c r="DO2" t="b">
-        <v>0</v>
-      </c>
-      <c r="DP2" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="DQ2" t="n">
-        <v>1779082531</v>
-      </c>
-      <c r="DR2" t="inlineStr">
-        <is>
-          <t>HKG</t>
-        </is>
-      </c>
-      <c r="DS2" t="inlineStr">
-        <is>
-          <t>PREPRE</t>
-        </is>
-      </c>
-      <c r="DT2" t="b">
-        <v>0</v>
-      </c>
-      <c r="DU2" t="n">
-        <v>946949400000</v>
-      </c>
-      <c r="DV2" t="n">
-        <v>0</v>
-      </c>
-      <c r="DW2" t="inlineStr">
-        <is>
-          <t>1.26 - 1.28</t>
-        </is>
-      </c>
-      <c r="DX2" t="inlineStr">
-        <is>
-          <t>HKSE</t>
-        </is>
-      </c>
-      <c r="DY2" t="n">
-        <v>7502</v>
-      </c>
-      <c r="DZ2" t="n">
-        <v>0.65</v>
-      </c>
-      <c r="EA2" t="n">
-        <v>1.031746</v>
-      </c>
-      <c r="EB2" t="inlineStr">
-        <is>
-          <t>0.63 - 1.68</t>
-        </is>
-      </c>
-      <c r="EC2" t="n">
-        <v>-0.39999998</v>
-      </c>
-      <c r="ED2" t="n">
-        <v>-0.23809522</v>
-      </c>
-      <c r="EE2" t="n">
-        <v>75.34247000000001</v>
-      </c>
-      <c r="EF2" t="n">
-        <v>1743421498</v>
-      </c>
-      <c r="EG2" t="n">
-        <v>1743421498</v>
-      </c>
-      <c r="EH2" t="b">
-        <v>0</v>
-      </c>
-      <c r="EI2" t="n">
-        <v>-4.4</v>
       </c>
       <c r="EJ2" t="inlineStr"/>
     </row>
